--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E690AC-FC46-4F6B-AAC8-19ED7389204B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D999F1F1-1590-4A01-B7D0-0B8CCCF36B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="519">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1584,6 +1584,33 @@
   </si>
   <si>
     <t>tudo ocorreu corretamente sem erros.</t>
+  </si>
+  <si>
+    <t>Confirmação de pagamento imediata</t>
+  </si>
+  <si>
+    <t>O requisito não especifica o comportamento caso ocorra uma falha de comunicação com o gateway de pagamento durante a confirmação.</t>
+  </si>
+  <si>
+    <t>Qual mensagem deve ser exibida ao usuário e qual o status do pedido se a transação do cartão sofrer timeout?</t>
+  </si>
+  <si>
+    <t>Não define quais tipos exatos de documentos são aceitos para comprovação da meia-entrada (se apenas carteira estudantil física ou digital também).</t>
+  </si>
+  <si>
+    <t>Quais documentos específicos são aceitos na bilheteria para validar a meia-entrada digital?</t>
+  </si>
+  <si>
+    <t>Validar se o sistema CineLume cumpre todas as Regras de Negócio especificadas no REQUISITOS.md e está apto para lançamento.</t>
+  </si>
+  <si>
+    <t>Fluxo completo de compra de ingressos, seleção de assentos, itens da bomboniere, aplicação de cupons, validação de formulários e regras de pagamento.</t>
+  </si>
+  <si>
+    <t>Funcionalidades de painel administrativo do cinema e integração real com gateway de pagamento bancário externo.</t>
+  </si>
+  <si>
+    <t>Apresentar documento de comprovante na entrada</t>
   </si>
 </sst>
 </file>
@@ -4020,25 +4047,45 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
@@ -4174,13 +4221,17 @@
       <c r="A4" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="23" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="23" t="s">
+        <v>516</v>
+      </c>
       <c r="C5" s="10" t="s">
         <v>113</v>
       </c>
@@ -4189,13 +4240,17 @@
       <c r="A6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="23" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>442</v>
+      </c>
       <c r="C7" s="10" t="s">
         <v>116</v>
       </c>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D999F1F1-1590-4A01-B7D0-0B8CCCF36B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7324CAA6-96CD-4C35-9188-DA3734A96DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="537">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1611,6 +1611,60 @@
   </si>
   <si>
     <t>Apresentar documento de comprovante na entrada</t>
+  </si>
+  <si>
+    <t>Garante a cobertura de caixa preta, caixa branca e verificação de requisitos não-funcionais exigidos nas missões do projeto.</t>
+  </si>
+  <si>
+    <t>Partição de Equivalência Análise de Valor Limite e Adivinhação de Erro.</t>
+  </si>
+  <si>
+    <t>navegador edge, usando vscode.</t>
+  </si>
+  <si>
+    <t>Sistema inicializado no navegador e aprovação nas verificações do Smoke Test</t>
+  </si>
+  <si>
+    <t>Execução de todos os casos de teste previstos, registro de bugs com evidências e correção bem-sucedida de pelo menos um bug.</t>
+  </si>
+  <si>
+    <t>Esquecer de commitar após a missão.</t>
+  </si>
+  <si>
+    <t>Essencial para validar todas as regras do REQUISITOS.md</t>
+  </si>
+  <si>
+    <t>Utilizado na Missão 6 para garantir que a correção de bug não quebrou o sistema.</t>
+  </si>
+  <si>
+    <t>Para retestar e confirmar a correção do bug</t>
+  </si>
+  <si>
+    <t>Utilizado na Missão 3 para encontrar falhas não mapeadas no fluxo livre.</t>
+  </si>
+  <si>
+    <t>Validar se o fluxo completo do sistema atende aos critérios de aceitação do cliente descritos no REQUISITOS.md.</t>
+  </si>
+  <si>
+    <t>Validar o tempo de resposta do sistema ao carregar a listagem de filmes.</t>
+  </si>
+  <si>
+    <t>Escopo focado em validações funcionais básicas.</t>
+  </si>
+  <si>
+    <t>Verificar o comportamento do sistema com múltiplos cliques simultâneos no mapa de assentos.</t>
+  </si>
+  <si>
+    <t>Volume de dados reduzido para esta versão do projeto.</t>
+  </si>
+  <si>
+    <t>Verificar inputs contra injeções de script (XSS) e validação de dados de formulário.</t>
+  </si>
+  <si>
+    <t>Testar a recuperação do carrinho de compras em caso de atualização da página.</t>
+  </si>
+  <si>
+    <t>Garantir navegação básica por teclado e contraste adequado nos botões principais.</t>
   </si>
 </sst>
 </file>
@@ -4259,13 +4313,17 @@
       <c r="A8" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="23" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="9"/>
+      <c r="B9" s="23" t="s">
+        <v>515</v>
+      </c>
       <c r="C9" s="10" t="s">
         <v>119</v>
       </c>
@@ -4274,7 +4332,9 @@
       <c r="A10" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="9"/>
+      <c r="B10" s="23" t="s">
+        <v>520</v>
+      </c>
       <c r="C10" s="10" t="s">
         <v>121</v>
       </c>
@@ -4283,7 +4343,9 @@
       <c r="A11" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="9"/>
+      <c r="B11" s="23" t="s">
+        <v>521</v>
+      </c>
       <c r="C11" s="10" t="s">
         <v>123</v>
       </c>
@@ -4292,7 +4354,9 @@
       <c r="A12" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="23" t="s">
+        <v>522</v>
+      </c>
       <c r="C12" s="10" t="s">
         <v>125</v>
       </c>
@@ -4301,7 +4365,9 @@
       <c r="A13" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="23" t="s">
+        <v>523</v>
+      </c>
       <c r="C13" s="10" t="s">
         <v>127</v>
       </c>
@@ -4310,7 +4376,9 @@
       <c r="A14" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="9"/>
+      <c r="B14" s="23" t="s">
+        <v>524</v>
+      </c>
       <c r="C14" s="10" t="s">
         <v>129</v>
       </c>
@@ -4335,85 +4403,133 @@
       <c r="A19" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>529</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7324CAA6-96CD-4C35-9188-DA3734A96DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830FCDED-FEDD-4FDF-B4E8-BBE80985271E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="637">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1665,6 +1665,306 @@
   </si>
   <si>
     <t>Garantir navegação básica por teclado e contraste adequado nos botões principais.</t>
+  </si>
+  <si>
+    <t>Ca01.1</t>
+  </si>
+  <si>
+    <t>Cadastro com nome válido</t>
+  </si>
+  <si>
+    <t>Acessar a página de dados do comprador</t>
+  </si>
+  <si>
+    <t>Digitar o nome no campo correspondente/Clicar em avançar</t>
+  </si>
+  <si>
+    <t>nome: joão andrade</t>
+  </si>
+  <si>
+    <t>Campo aceite sem erros</t>
+  </si>
+  <si>
+    <t>Campo aceito e sem mensagens de erro exibidas.</t>
+  </si>
+  <si>
+    <t>ca02.1</t>
+  </si>
+  <si>
+    <t>E-mail válido no cadastro</t>
+  </si>
+  <si>
+    <t>Digitar e-mail correto/Clicar em avançar</t>
+  </si>
+  <si>
+    <t>email: lindo@gmail.com</t>
+  </si>
+  <si>
+    <t>E-mail aceite pelo sistema</t>
+  </si>
+  <si>
+    <t>ca02.2</t>
+  </si>
+  <si>
+    <t>E-mail sem o caractere @</t>
+  </si>
+  <si>
+    <t>Digitar e-mail sem @/Clicar em confirmar</t>
+  </si>
+  <si>
+    <t>email: lindauvo@gmail.coom</t>
+  </si>
+  <si>
+    <t>Mensagem de erro exibida indicando formato inválido</t>
+  </si>
+  <si>
+    <t>ca03.1</t>
+  </si>
+  <si>
+    <t>Seleção de assento livre</t>
+  </si>
+  <si>
+    <t>Estar no mapa de assentos da sessão escolhida</t>
+  </si>
+  <si>
+    <t>Clicar num assento livre (cor verde)/Verificar atualização no resumo</t>
+  </si>
+  <si>
+    <t>assento: B04</t>
+  </si>
+  <si>
+    <t>Assento marcado como selecionado e valor somado</t>
+  </si>
+  <si>
+    <t>ca04.1</t>
+  </si>
+  <si>
+    <t>Tentativa de selecionar assento ocupado</t>
+  </si>
+  <si>
+    <t>Estar no mapa de assentos da sessão</t>
+  </si>
+  <si>
+    <t>Clicar num assento já ocupado (cor vermelha)</t>
+  </si>
+  <si>
+    <t>Assento: A02 (ocupado)</t>
+  </si>
+  <si>
+    <t>Sistema impede a seleção e avisa que o assento está indisponível</t>
+  </si>
+  <si>
+    <t>ca05.1</t>
+  </si>
+  <si>
+    <t>Seleção de modalidade meia-entrada</t>
+  </si>
+  <si>
+    <t>Estar na escolha de tipos de ingressos</t>
+  </si>
+  <si>
+    <t>Selecionar meia-entrada para o ingresso</t>
+  </si>
+  <si>
+    <t>Modalidade: Meia</t>
+  </si>
+  <si>
+    <t>Sistema exige comprovação ou aplica o desconto correto</t>
+  </si>
+  <si>
+    <t>ca06.1</t>
+  </si>
+  <si>
+    <t>Adicionar item da bomboniere</t>
+  </si>
+  <si>
+    <t>Estar na aba da bomboniere</t>
+  </si>
+  <si>
+    <t>Escolher um combo/Clicar em adicionar ao carrinho</t>
+  </si>
+  <si>
+    <t>Item: Pipoca pequena</t>
+  </si>
+  <si>
+    <t>Item adicionado ao carrinho com valor somado ao total</t>
+  </si>
+  <si>
+    <t>ca07.1</t>
+  </si>
+  <si>
+    <t>Aplicação de cupom válido</t>
+  </si>
+  <si>
+    <t>Estar na tela de pagamento com itens no carrinho</t>
+  </si>
+  <si>
+    <t>Digitar cupom ativo/Clicar em aplicar</t>
+  </si>
+  <si>
+    <t>Cupom: CINEMA10</t>
+  </si>
+  <si>
+    <t>Desconto aplicado sobre o valor total da compra</t>
+  </si>
+  <si>
+    <t>ca07.2</t>
+  </si>
+  <si>
+    <t>Aplicação de cupom inválido</t>
+  </si>
+  <si>
+    <t>Estar na tela de pagamento</t>
+  </si>
+  <si>
+    <t>Digitar cupom inexistente\n2. Clicar em aplicar</t>
+  </si>
+  <si>
+    <t>Cupom: INVALIDO99</t>
+  </si>
+  <si>
+    <t>Mensagem de erro informando que o cupom é inválido</t>
+  </si>
+  <si>
+    <t>ca08.1</t>
+  </si>
+  <si>
+    <t>Pagamento com cartão de crédito</t>
+  </si>
+  <si>
+    <t>Estar na etapa final de pagamento</t>
+  </si>
+  <si>
+    <t>Selecionar cartão/Preencher dados válidos/ Finalizar</t>
+  </si>
+  <si>
+    <t>Dados de cartão válidos</t>
+  </si>
+  <si>
+    <t>Compra aprovada e redirecionamento para confirmação</t>
+  </si>
+  <si>
+    <t>ca01.2</t>
+  </si>
+  <si>
+    <t>Nome com 1 caractere (abaixo do limite)</t>
+  </si>
+  <si>
+    <t>Estar no cadastro</t>
+  </si>
+  <si>
+    <t>Digitar nome com 1 letra/Avançar</t>
+  </si>
+  <si>
+    <t>Nome: B</t>
+  </si>
+  <si>
+    <t>Sistema rejeita por não atingir o limite mínimo</t>
+  </si>
+  <si>
+    <t>ca01.3</t>
+  </si>
+  <si>
+    <t>Nome com 2 caracteres (limite mínimo exato)</t>
+  </si>
+  <si>
+    <t>Digitar nome com 2 letras/Avançar</t>
+  </si>
+  <si>
+    <t>Nome: Je</t>
+  </si>
+  <si>
+    <t>Sistema aceita o campo por atingir o limite mínimo</t>
+  </si>
+  <si>
+    <t>ca09.1</t>
+  </si>
+  <si>
+    <t>Selecionar zero ingressos</t>
+  </si>
+  <si>
+    <t>Estar na selecção de bilhetes</t>
+  </si>
+  <si>
+    <t>Manter quantidade de ingressos em 0/ Tentar prosseguir</t>
+  </si>
+  <si>
+    <t>Quantidade: 0</t>
+  </si>
+  <si>
+    <t>Sistema impede o avanço e exige pelo menos 1 ingresso</t>
+  </si>
+  <si>
+    <t>ca10.1</t>
+  </si>
+  <si>
+    <t>Quantidade máxima permitida de ingressos</t>
+  </si>
+  <si>
+    <t>Selecionar o limite máximo de assentos permitidos</t>
+  </si>
+  <si>
+    <t>Quantidade: 10 ingressos</t>
+  </si>
+  <si>
+    <t>Sistema aceita a seleção até ao limite máximo</t>
+  </si>
+  <si>
+    <t>ca10.2</t>
+  </si>
+  <si>
+    <t>Quantidade acima do máximo permitido</t>
+  </si>
+  <si>
+    <t>Selecionar quantidade acima do teto permitido</t>
+  </si>
+  <si>
+    <t>Quantidade: 11 ingressos</t>
+  </si>
+  <si>
+    <t>Sistema bloqueia e exibe aviso sobre o limite máximo</t>
+  </si>
+  <si>
+    <t>E-mail validado e aceito pelo sistema.</t>
+  </si>
+  <si>
+    <t>Mensagem "Informe um e-mail válido" exibida corretamente.</t>
+  </si>
+  <si>
+    <t>Assento selecionado e valor somado ao resumo.</t>
+  </si>
+  <si>
+    <t>Sistema bloqueou a seleção de assento ocupado.</t>
+  </si>
+  <si>
+    <t>Modalidade meia-entrada aplicada corretamente.</t>
+  </si>
+  <si>
+    <t>Item adicionado ao carrinho com valor correto.</t>
+  </si>
+  <si>
+    <t>Desconto do cupom aplicado no valor total.</t>
+  </si>
+  <si>
+    <t>Aviso de cupom inválido exibido com sucesso.</t>
+  </si>
+  <si>
+    <t>Pagamento processado e tela de confirmação exibida.</t>
+  </si>
+  <si>
+    <t>Sistema rejeitou o cadastro por tamanho inválido.</t>
+  </si>
+  <si>
+    <t>Sistema aceitou o nome no limite mínimo.</t>
+  </si>
+  <si>
+    <t>Sistema impediu o avanço com 0 ingressos.</t>
+  </si>
+  <si>
+    <t>Seleção permitida até o teto máximo de assentos.</t>
+  </si>
+  <si>
+    <t>Sistema bloqueou a seleção acima do limite e exibiu aviso.</t>
   </si>
 </sst>
 </file>
@@ -2901,7 +3201,7 @@
       </c>
       <c r="B5" s="19">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -2910,7 +3210,7 @@
       </c>
       <c r="B6" s="19">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2946,7 +3246,7 @@
       </c>
       <c r="B10" s="20">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -2955,7 +3255,7 @@
       </c>
       <c r="B11" s="19">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -4682,288 +4982,648 @@
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
+      <c r="B6" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>543</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
+      <c r="B8" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
+      <c r="B11" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
+      <c r="B12" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
+      <c r="B13" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
+      <c r="B14" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
+      <c r="B15" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
+      <c r="B16" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
+      <c r="B17" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
+      <c r="B18" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
+      <c r="B19" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
+      <c r="B20" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
     </row>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830FCDED-FEDD-4FDF-B4E8-BBE80985271E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1720AFC0-3DE2-4A21-9528-1206181FDAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="654">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1965,6 +1965,57 @@
   </si>
   <si>
     <t>Sistema bloqueou a seleção acima do limite e exibiu aviso.</t>
+  </si>
+  <si>
+    <t>evidencia_ct01.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct02.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct03.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct04.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct05.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct06.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct07.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct08.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct09.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct10.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct11.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct12.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct13.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct14.png</t>
+  </si>
+  <si>
+    <t>evidencia_ct15.png</t>
+  </si>
+  <si>
+    <t>Erro no cálculo do valor total ao selecionar múltiplos assentos</t>
+  </si>
+  <si>
+    <t>Aceder à sessão/Selecionar 2 assentos normais/ Verificar o valor total no resumo do carrinho</t>
   </si>
 </sst>
 </file>
@@ -2114,9 +2165,6 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2162,6 +2210,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2437,206 +2488,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2662,330 +2713,330 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3044,100 +3095,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3180,263 +3231,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Bloqueado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Não executado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Alta")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <f>COUNTIF('6_Bugs'!N6:N35,"Corrigido*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <f>COUNTIF('7_Nao_Funcionais'!H6:H20,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="9" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="9" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="10" t="s">
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="9" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3484,147 +3535,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3653,382 +3704,382 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>494</v>
       </c>
     </row>
@@ -4048,92 +4099,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <v>46323</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <v>0.80208333333333337</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4158,154 +4209,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="22" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="22" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="22" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="22" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="22" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>509</v>
       </c>
     </row>
@@ -4352,174 +4403,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>433</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>510</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="22" t="s">
         <v>511</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="22" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4562,272 +4613,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="22" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>521</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>523</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>524</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>435</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="22" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="22" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>529</v>
       </c>
     </row>
@@ -4883,1224 +4934,1254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>538</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="22" t="s">
         <v>539</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="22" t="s">
         <v>540</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="22" t="s">
         <v>541</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="22" t="s">
         <v>542</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>544</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="22" t="s">
         <v>545</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="14" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>587</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>646</v>
+      </c>
     </row>
     <row r="16" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="M16" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="17" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="M17" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="18" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="19" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="M19" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="20" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="M20" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6180,678 +6261,694 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="14" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="B6" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6937,300 +7034,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7289,356 +7386,356 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1720AFC0-3DE2-4A21-9528-1206181FDAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1761A50F-B26B-48A0-A26E-2099D6B04481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="687">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2016,6 +2016,105 @@
   </si>
   <si>
     <t>Aceder à sessão/Selecionar 2 assentos normais/ Verificar o valor total no resumo do carrinho</t>
+  </si>
+  <si>
+    <t>Assentos: B04 e B05</t>
+  </si>
+  <si>
+    <t>O valor total deve somar exatamente o preço de dois ingressos.</t>
+  </si>
+  <si>
+    <t>O sistema soma apenas o valor de um único ingresso no total do carrinho.</t>
+  </si>
+  <si>
+    <t>Campo de e-mail aceita caracteres inválidos sem o símbolo @</t>
+  </si>
+  <si>
+    <t>Chegar à etapa de dados do comprador/ Digitar um e-mail sem o caractere '@'/Clicar em avançar</t>
+  </si>
+  <si>
+    <t>E-mail: lindoemail.com</t>
+  </si>
+  <si>
+    <t>O sistema deve bloquear e exibir mensagem de formato inválido.</t>
+  </si>
+  <si>
+    <t>O sistema aceita o avanço sem validar o formato do e-mail.</t>
+  </si>
+  <si>
+    <t>Possibilidade de selecionar assento já ocupado</t>
+  </si>
+  <si>
+    <t>Abrir o mapa de assentos/Clicar diretamente num assento marcado como ocupado</t>
+  </si>
+  <si>
+    <t>Assento: A01 (ocupado)</t>
+  </si>
+  <si>
+    <t>O sistema deve impedir a marcação e emitir aviso de indisponibilidade.</t>
+  </si>
+  <si>
+    <t>O assento ocupado fica selecionado e é contabilizado na compra.</t>
+  </si>
+  <si>
+    <t>Cupom de desconto expirado é aplicado com sucesso</t>
+  </si>
+  <si>
+    <t>Ir para a tela de pagamento/ Inserir um cupom com data de validade vencida/Clicar em aplicar</t>
+  </si>
+  <si>
+    <t>Cupom: PROMO2023</t>
+  </si>
+  <si>
+    <t>O sistema deve recusar o cupom e exibir mensagem de expiração.</t>
+  </si>
+  <si>
+    <t>O desconto é aplicado normalmente no valor final da compra.</t>
+  </si>
+  <si>
+    <t>Estouro de limite máximo de ingressos por transação</t>
+  </si>
+  <si>
+    <t>Na seleção de bilhetes, escolher 11 assentos/ Tentar prosseguir</t>
+  </si>
+  <si>
+    <t>O sistema deve bloquear e alertar sobre o limite máximo por compra.</t>
+  </si>
+  <si>
+    <t>O sistema permite prosseguir para o pagamento sem restrições.</t>
+  </si>
+  <si>
+    <t>Falha de responsividade no botão de confirmação em telas menores</t>
+  </si>
+  <si>
+    <t>Reduzir a janela do navegador para tamanho mobile/ Aceder à tela de finalização</t>
+  </si>
+  <si>
+    <t>Resolução simulada de telemóvel</t>
+  </si>
+  <si>
+    <t>O botão de confirmar pagamento deve adaptar-se visivelmente ao ecrã.</t>
+  </si>
+  <si>
+    <t>O botão fica parcialmente oculto fora da área visível do ecrã.</t>
+  </si>
+  <si>
+    <t>bug_01.png</t>
+  </si>
+  <si>
+    <t>bug_02.png</t>
+  </si>
+  <si>
+    <t>bug_03.png</t>
+  </si>
+  <si>
+    <t>bug_04.png</t>
+  </si>
+  <si>
+    <t>bug_05.png</t>
+  </si>
+  <si>
+    <t>bug_06.png</t>
   </si>
 </sst>
 </file>
@@ -3315,7 +3414,7 @@
       </c>
       <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -3324,7 +3423,7 @@
       </c>
       <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -3342,7 +3441,7 @@
       </c>
       <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -3351,7 +3450,7 @@
       </c>
       <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -6364,7 +6463,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>231</v>
       </c>
@@ -6392,107 +6491,259 @@
       <c r="I6" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J6" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1761A50F-B26B-48A0-A26E-2099D6B04481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EB540C-AF47-4D45-B5AF-5207249C2ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="721">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2115,6 +2115,108 @@
   </si>
   <si>
     <t>bug_06.png</t>
+  </si>
+  <si>
+    <t>Tempo de carregamento inicial do DOM da página</t>
+  </si>
+  <si>
+    <t>DevTools Network tab: carregamento limpo (Ctrl+F5)</t>
+  </si>
+  <si>
+    <t>320 ms</t>
+  </si>
+  <si>
+    <t>ate 2000 ms</t>
+  </si>
+  <si>
+    <t>Tempo para processar renderização de 500 assentos simultâneos</t>
+  </si>
+  <si>
+    <t>Console: console.time + loop para gerar elementos DOM de assentos</t>
+  </si>
+  <si>
+    <t>150 ms</t>
+  </si>
+  <si>
+    <t>ate 1000 ms</t>
+  </si>
+  <si>
+    <t>Comportamento ao efetuar 50 cliques consecutivos no botão de adicionar item</t>
+  </si>
+  <si>
+    <t>Console: script de repetição rápida com evento .click()</t>
+  </si>
+  <si>
+    <t>Sem travamento ou exceção</t>
+  </si>
+  <si>
+    <t>Manter estabilidade da interface</t>
+  </si>
+  <si>
+    <t>Suporte a entrada de string longa com 255 caracteres no campo Nome</t>
+  </si>
+  <si>
+    <t>Inserção de string com 255 caracteres via console no input</t>
+  </si>
+  <si>
+    <t>Texto truncado/limitado corretamente</t>
+  </si>
+  <si>
+    <t>Não quebrar o layout nem estourar o banco local</t>
+  </si>
+  <si>
+    <t>Resistência a injeção de scripts (XSS) no campo de Nome</t>
+  </si>
+  <si>
+    <t>Digitação do payload &lt;script&gt;alert('xss')&lt;/script&gt; no formulário</t>
+  </si>
+  <si>
+    <t>String tratada como texto puro</t>
+  </si>
+  <si>
+    <t>Não executar scripts no navegador</t>
+  </si>
+  <si>
+    <t>Manutenção dos itens no carrinho após recarregar a página (F5)</t>
+  </si>
+  <si>
+    <t>Adicionar itens ao carrinho e atualizar a página</t>
+  </si>
+  <si>
+    <t>Estado do carrinho preservado via localStorage</t>
+  </si>
+  <si>
+    <t>Manter dados informados pelo utilizador</t>
+  </si>
+  <si>
+    <t>Navegação completa no formulário e seleção via teclado (Tab/Espaço)</t>
+  </si>
+  <si>
+    <t>Navegação manual utilizando apenas a tecla Tab e Enter</t>
+  </si>
+  <si>
+    <t>Foco visível em todos os campos interativos</t>
+  </si>
+  <si>
+    <t>Acessibilidade total via teclado</t>
+  </si>
+  <si>
+    <t>nf_02.png</t>
+  </si>
+  <si>
+    <t>nf_03.png</t>
+  </si>
+  <si>
+    <t>nf_04.png</t>
+  </si>
+  <si>
+    <t>nf_05.png</t>
+  </si>
+  <si>
+    <t>nf_06.png</t>
+  </si>
+  <si>
+    <t>nf_07.png</t>
   </si>
 </sst>
 </file>
@@ -3468,7 +3570,7 @@
       </c>
       <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -7356,117 +7458,215 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>274</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="8" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>275</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="8" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>276</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>277</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="8" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>278</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="8" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>279</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="8" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>280</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>720</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EB540C-AF47-4D45-B5AF-5207249C2ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329BB69E-D7C1-4D35-B2B5-778483F6BD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="740">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2217,6 +2217,63 @@
   </si>
   <si>
     <t>nf_07.png</t>
+  </si>
+  <si>
+    <t>condição verdadeira</t>
+  </si>
+  <si>
+    <t>validarNome("João")</t>
+  </si>
+  <si>
+    <t>true (RN13: mínimo de 3 caracteres)</t>
+  </si>
+  <si>
+    <t>mail.includes('@') &amp;&amp; email.includes('.')</t>
+  </si>
+  <si>
+    <t>validarEmail("lindo@email.com")</t>
+  </si>
+  <si>
+    <t>true (RN02: formato de e-mail válido)</t>
+  </si>
+  <si>
+    <t>Condição falsa (ausência de @)</t>
+  </si>
+  <si>
+    <t>validarEmail("lindoemail.com")</t>
+  </si>
+  <si>
+    <t>false (RN02: e-mail sem @)</t>
+  </si>
+  <si>
+    <t>qtd &gt; 0 &amp;&amp; qtd &lt;= 10</t>
+  </si>
+  <si>
+    <t>Condição verdadeira (dentro do limite)</t>
+  </si>
+  <si>
+    <t>validarQuantidadeIngressos</t>
+  </si>
+  <si>
+    <t>true (RN10: permitido entre 1 e 10 ingressos)</t>
+  </si>
+  <si>
+    <t>Condição falsa (abaixo do limite mínimo)</t>
+  </si>
+  <si>
+    <t>validarQuantidadeIngressos(0)</t>
+  </si>
+  <si>
+    <t>false (RN10: mínimo de 1 ingresso)</t>
+  </si>
+  <si>
+    <t>Condição falsa (acima do limite máximo)</t>
+  </si>
+  <si>
+    <t>validarQuantidadeIngressos(11)</t>
+  </si>
+  <si>
+    <t>false (RN10: máximo de 10 ingressos)</t>
   </si>
 </sst>
 </file>
@@ -3588,7 +3645,7 @@
       </c>
       <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -6800,7 +6857,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>236</v>
       </c>
@@ -7908,89 +7965,189 @@
       </c>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="J6" s="8"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>443</v>
+      </c>
       <c r="J7" s="8"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>222</v>
+      </c>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>222</v>
+      </c>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329BB69E-D7C1-4D35-B2B5-778483F6BD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41958A5D-8691-419F-97C3-84D3B01D112B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="764">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2274,6 +2274,78 @@
   </si>
   <si>
     <t>false (RN10: máximo de 10 ingressos)</t>
+  </si>
+  <si>
+    <t>Nome com 3 ou mais caracteres é válido</t>
+  </si>
+  <si>
+    <t>testar('AT01', 'Nome válido', validarNome('Carlos'), true);</t>
+  </si>
+  <si>
+    <t>Nome com menos de 3 caracteres é recusado</t>
+  </si>
+  <si>
+    <t>testar('AT02', 'Nome curto', validarNome('Zé'), false);</t>
+  </si>
+  <si>
+    <t>E-mail sem o símbolo @ deve ser recusado</t>
+  </si>
+  <si>
+    <t>testar('AT03', 'E-mail sem @', validarEmail('clienteemail.com'), false);</t>
+  </si>
+  <si>
+    <t>Quantidade dentro do limite permitido (1 a 10)</t>
+  </si>
+  <si>
+    <t>testar('AT04', 'Qtd válida', validarQuantidadeIngressos(5), true);</t>
+  </si>
+  <si>
+    <t>Quantidade acima do teto de 10 ingressos</t>
+  </si>
+  <si>
+    <t>testar('AT05', 'Qtd acima limite', validarQuantidadeIngressos(11), false);</t>
+  </si>
+  <si>
+    <t>Cupom de desconto expirado</t>
+  </si>
+  <si>
+    <t>testar('AT06', 'Cupom expirado', validarCupom('PROMO2023'), false);</t>
+  </si>
+  <si>
+    <t>Tentativa de seleção de assento já ocupado</t>
+  </si>
+  <si>
+    <t>testar('AT07', 'Assento ocupado', validarAssento('A01'), false);</t>
+  </si>
+  <si>
+    <t>Cálculo correto do total para múltiplos assentos</t>
+  </si>
+  <si>
+    <t>testar('AT08', 'Cálculo total', calcularTotal(2, 20.0), 40.0);</t>
+  </si>
+  <si>
+    <t>40.0</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>regras.js</t>
+  </si>
+  <si>
+    <t>calcularTotal</t>
+  </si>
+  <si>
+    <t>A função somava apenas o preço unitário de um único ingresso em vez de multiplicar pela quantidade selecionada.</t>
+  </si>
+  <si>
+    <t>Ajuste na lógica de cálculo para multiplicar o valor unitário pela quantidade total de assentos escolhidos.</t>
+  </si>
+  <si>
+    <t>AT01 a AT07</t>
+  </si>
+  <si>
+    <t>passaram</t>
   </si>
 </sst>
 </file>
@@ -3040,105 +3112,227 @@
       <c r="A6" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -3404,16 +3598,36 @@
       <c r="A5" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>448</v>
+      </c>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -3654,7 +3868,7 @@
       </c>
       <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -3663,7 +3877,7 @@
       </c>
       <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -3672,7 +3886,7 @@
       </c>
       <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41958A5D-8691-419F-97C3-84D3B01D112B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65F75BD-148B-451D-AF0B-C3169280509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="765">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2346,6 +2346,9 @@
   </si>
   <si>
     <t>passaram</t>
+  </si>
+  <si>
+    <t>9a6c1f9</t>
   </si>
 </sst>
 </file>
@@ -3628,7 +3631,9 @@
       <c r="K5" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="L5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65F75BD-148B-451D-AF0B-C3169280509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BE34A1-A0AD-446C-A553-B27EA9897F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="772">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2349,6 +2349,27 @@
   </si>
   <si>
     <t>9a6c1f9</t>
+  </si>
+  <si>
+    <t>O CineLume v1.0 passou por um processo completo de testes, cobrindo a parte funcional, estrutural, não funcional e automatizada. A aplicação surpreendeu positivamente na performance e nos testes de carga, mas encontrámos falhas críticas nas regras de negócio e nos cálculos que exigem correção antes de o sistema ir para as mãos dos utilizadores.</t>
+  </si>
+  <si>
+    <t>BUG-03: O sistema permite selecionar assentos que já estão ocupados no mapa da sala, o que pode gerar graves problemas de overbooking e confusão no atendimento.</t>
+  </si>
+  <si>
+    <t>BUG-01: Erro crítico no carrinho de compras, onde o cálculo do valor total para vários bilhetes acaba por ignorar a quantidade e soma apenas o preço de um único ingresso.</t>
+  </si>
+  <si>
+    <t>BUG-04: Cupões de desconto com prazos de validade já expirados continuam a ser aplicados com sucesso, o que impacta diretamente a receita das vendas.</t>
+  </si>
+  <si>
+    <t>Apesar de a aplicação estar tecnicamente estável e rápida, as falhas detetadas na escolha de lugares e nos pagamentos representam um risco operacional e financeiro demasiado alto para avançarmos sem correções imediatas.</t>
+  </si>
+  <si>
+    <t>Ficaram de fora os testes de integração com os gateways de pagamento reais. O risco é termos comportamentos inesperados ou falhas de comunicação com as operadoras financeiras no momento do checkout em produção.</t>
+  </si>
+  <si>
+    <t>Numa próxima oportunidade, traria a automação de testes de ponta a ponta para mais cedo no cronograma e criaria cenários de carga ainda mais agressivos para simular picos de acessos em dias de estreia.</t>
   </si>
 </sst>
 </file>
@@ -3905,7 +3926,9 @@
       <c r="A26" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B26" s="24"/>
+      <c r="B26" s="24" t="s">
+        <v>765</v>
+      </c>
       <c r="C26" s="24"/>
       <c r="D26" s="9" t="s">
         <v>395</v>
@@ -3915,28 +3938,36 @@
       <c r="A27" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B27" s="24"/>
+      <c r="B27" s="24" t="s">
+        <v>766</v>
+      </c>
       <c r="C27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="24" t="s">
+        <v>767</v>
+      </c>
       <c r="C28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="24"/>
+      <c r="B29" s="24" t="s">
+        <v>768</v>
+      </c>
       <c r="C29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B30" s="24"/>
+      <c r="B30" s="24" t="s">
+        <v>450</v>
+      </c>
       <c r="C30" s="24"/>
       <c r="D30" s="9" t="s">
         <v>400</v>
@@ -3946,7 +3977,9 @@
       <c r="A31" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B31" s="24"/>
+      <c r="B31" s="24" t="s">
+        <v>769</v>
+      </c>
       <c r="C31" s="24"/>
       <c r="D31" s="9" t="s">
         <v>402</v>
@@ -3956,14 +3989,18 @@
       <c r="A32" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B32" s="24"/>
+      <c r="B32" s="24" t="s">
+        <v>770</v>
+      </c>
       <c r="C32" s="24"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="24"/>
+      <c r="B33" s="24" t="s">
+        <v>771</v>
+      </c>
       <c r="C33" s="24"/>
     </row>
   </sheetData>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BE34A1-A0AD-446C-A553-B27EA9897F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BC2F3A-39A8-4738-90C4-ADB9C61685F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="794">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -2370,6 +2370,72 @@
   </si>
   <si>
     <t>Numa próxima oportunidade, traria a automação de testes de ponta a ponta para mais cedo no cronograma e criaria cenários de carga ainda mais agressivos para simular picos de acessos em dias de estreia.</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Quais são as melhores técnicas para criar casos de teste baseados em particionamento de equivalência e análise de valor limite para validação de e-mail?</t>
+  </si>
+  <si>
+    <t>Explicou os conceitos teóricos de divisão de classes válidas e inválidas para campos de texto.</t>
+  </si>
+  <si>
+    <t>A ideia de organizar as colunas e separar bem os cenários positivos dos negativos.</t>
+  </si>
+  <si>
+    <t>Mudei os exemplos genéricos da IA para baterem certo com as regras do CineLume.</t>
+  </si>
+  <si>
+    <t>não usei ia</t>
+  </si>
+  <si>
+    <t>Quais são os pontos principais que devo avaliar para testar a performance e a segurança básica de uma aplicação web local?</t>
+  </si>
+  <si>
+    <t>Destacou a importância de medir o tempo de resposta e olhar os dados no console.</t>
+  </si>
+  <si>
+    <t>Os critérios para preencher os testes de carga e desempenho.</t>
+  </si>
+  <si>
+    <t>Adaptei tudo para os testes reais que fiz no navegador a testar o sistema.</t>
+  </si>
+  <si>
+    <t>Podes me dar um exemplo simples de como funciona uma função de teste unitário em JavaScript para comparar valores?</t>
+  </si>
+  <si>
+    <t>Mostrou uma estrutura básica de validação de resultados esperados versus obtidos.</t>
+  </si>
+  <si>
+    <t>A lógica para montar a tabela de resultados no HTML.</t>
+  </si>
+  <si>
+    <t>Reescrevi e ajustei para chamar as funções reais do regras.js.</t>
+  </si>
+  <si>
+    <t>Como posso escrever um resumo executivo de um relatório de testes recomendando liberar o sistema, mas com ressalvas?</t>
+  </si>
+  <si>
+    <t>Deu dicas de como equilibrar os pontos positivos com os bugs encontrados.</t>
+  </si>
+  <si>
+    <t>A forma de organizar o texto de forma profissional.</t>
+  </si>
+  <si>
+    <t>Coloquei os bugs reais do nosso projeto (assentos e pagamentos) e a decisão final do CineLume.</t>
+  </si>
+  <si>
+    <t>Como posso verificar de forma simples se a correção de um bug num formulário não afetou outras partes do sistema?</t>
+  </si>
+  <si>
+    <t>Explicou o conceito de teste de regressão e sugeriu reexecutar os cenários afetados.</t>
+  </si>
+  <si>
+    <t>A ideia de focar os testes nas funções ao redor da correção.</t>
+  </si>
+  <si>
+    <t>Executei manualmente os testes no sistema para validar a correção do BUG-01 e garantir que tudo funcionava.</t>
   </si>
 </sst>
 </file>
@@ -2517,7 +2583,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2567,6 +2633,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="47" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4081,82 +4150,150 @@
         <v>411</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>777</v>
+      </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>781</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>777</v>
+      </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>789</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -4697,7 +4834,9 @@
       <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="25">
+        <v>46296.013429398146</v>
+      </c>
       <c r="C11" s="9" t="s">
         <v>60</v>
       </c>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BC2F3A-39A8-4738-90C4-ADB9C61685F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8036C6DF-3769-4CF6-818E-92F53E12D7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="11784" windowHeight="12216" tabRatio="500" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
